--- a/data/trans_bre/P2A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 9,3</t>
+          <t>-21,21; 7,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 23,99</t>
+          <t>-17,17; 23,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 11,7</t>
+          <t>-20,48; 10,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 12,86</t>
+          <t>-19,52; 12,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,27; 39,89</t>
+          <t>-52,77; 37,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,93; 83,84</t>
+          <t>-36,78; 89,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-40,17; 29,98</t>
+          <t>-38,18; 28,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 30,62</t>
+          <t>-34,91; 29,54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,47; 3,53</t>
+          <t>-24,0; 3,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 13,16</t>
+          <t>-16,03; 13,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 21,19</t>
+          <t>-3,92; 22,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 19,64</t>
+          <t>-5,05; 18,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,92; 9,4</t>
+          <t>-45,66; 12,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,61; 44,11</t>
+          <t>-36,0; 46,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 85,52</t>
+          <t>-10,9; 88,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 29,01</t>
+          <t>-6,08; 27,64</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 12,49</t>
+          <t>-12,03; 12,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 21,37</t>
+          <t>-8,58; 20,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 13,57</t>
+          <t>-14,85; 14,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 8,66</t>
+          <t>-16,78; 8,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,92; 58,34</t>
+          <t>-36,54; 57,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 87,19</t>
+          <t>-22,08; 80,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 58,25</t>
+          <t>-39,54; 59,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 12,3</t>
+          <t>-20,99; 12,97</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 7,03</t>
+          <t>-17,91; 8,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 20,39</t>
+          <t>-12,29; 19,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 22,34</t>
+          <t>-11,89; 21,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 37,33</t>
+          <t>-3,09; 37,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,43; 21,57</t>
+          <t>-38,12; 24,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 72,79</t>
+          <t>-30,03; 68,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,4; 86,61</t>
+          <t>-28,25; 86,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 96,86</t>
+          <t>-4,03; 96,96</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 53,34</t>
+          <t>-11,05; 56,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 40,18</t>
+          <t>-9,79; 39,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 19,75</t>
+          <t>-17,8; 19,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 16,85</t>
+          <t>-2,52; 17,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 583,23</t>
+          <t>-31,43; 502,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 204,57</t>
+          <t>-24,61; 195,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-38,41; 66,62</t>
+          <t>-38,22; 72,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 20,3</t>
+          <t>-2,56; 21,65</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,74; 2,52</t>
+          <t>-25,79; 1,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 18,47</t>
+          <t>-15,83; 16,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 25,05</t>
+          <t>-15,1; 25,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 9,41</t>
+          <t>-18,41; 10,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,27; 11,2</t>
+          <t>-62,4; 7,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,22; 57,92</t>
+          <t>-32,73; 55,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 102,03</t>
+          <t>-33,83; 96,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 14,99</t>
+          <t>-23,87; 16,73</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 6,1</t>
+          <t>-15,04; 5,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 9,56</t>
+          <t>-11,36; 10,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 7,21</t>
+          <t>-11,13; 7,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 14,23</t>
+          <t>-6,11; 13,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 20,87</t>
+          <t>-35,6; 17,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,85; 30,63</t>
+          <t>-27,26; 30,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-33,9; 29,67</t>
+          <t>-33,02; 33,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 19,6</t>
+          <t>-6,92; 18,84</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 9,96</t>
+          <t>-12,38; 10,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 1,44</t>
+          <t>-15,53; 2,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 7,43</t>
+          <t>-9,7; 8,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 7,86</t>
+          <t>-5,93; 7,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,79; 27,73</t>
+          <t>-26,76; 29,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-46,11; 4,83</t>
+          <t>-44,16; 10,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,96; 26,74</t>
+          <t>-26,48; 30,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 9,71</t>
+          <t>-6,56; 8,8</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 0,33</t>
+          <t>-9,33; -0,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 5,1</t>
+          <t>-4,85; 4,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 5,22</t>
+          <t>-4,17; 5,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 7,67</t>
+          <t>-2,63; 7,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 1,02</t>
+          <t>-23,34; -0,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 15,46</t>
+          <t>-12,81; 14,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 16,36</t>
+          <t>-11,57; 17,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 10,43</t>
+          <t>-3,38; 10,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 7,89</t>
+          <t>-19,62; 8,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 23,58</t>
+          <t>-17,27; 24,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 10,88</t>
+          <t>-20,26; 11,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 12,41</t>
+          <t>-17,8; 13,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-52,77; 37,68</t>
+          <t>-51,25; 37,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,78; 89,69</t>
+          <t>-35,98; 90,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 28,68</t>
+          <t>-39,2; 28,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 29,54</t>
+          <t>-31,83; 31,57</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,0; 3,62</t>
+          <t>-23,78; 2,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 13,56</t>
+          <t>-16,27; 13,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 22,33</t>
+          <t>-4,68; 20,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 18,98</t>
+          <t>-6,05; 20,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,66; 12,27</t>
+          <t>-44,43; 7,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 46,84</t>
+          <t>-36,15; 45,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 88,42</t>
+          <t>-12,44; 84,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 27,64</t>
+          <t>-7,46; 29,35</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 12,11</t>
+          <t>-12,07; 13,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 20,84</t>
+          <t>-9,15; 21,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 14,5</t>
+          <t>-14,11; 15,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 8,67</t>
+          <t>-15,81; 9,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,54; 57,87</t>
+          <t>-37,97; 64,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 80,01</t>
+          <t>-23,77; 84,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-39,54; 59,38</t>
+          <t>-40,73; 68,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 12,97</t>
+          <t>-19,69; 13,21</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 8,29</t>
+          <t>-16,54; 9,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 19,63</t>
+          <t>-10,72; 21,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 21,9</t>
+          <t>-11,41; 21,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 37,9</t>
+          <t>-3,64; 37,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 24,71</t>
+          <t>-35,73; 31,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,03; 68,89</t>
+          <t>-24,37; 81,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 86,09</t>
+          <t>-28,23; 84,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 96,96</t>
+          <t>-4,95; 95,76</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 56,01</t>
+          <t>-13,17; 58,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 39,98</t>
+          <t>-9,35; 40,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 19,8</t>
+          <t>-15,9; 20,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 17,44</t>
+          <t>-2,49; 17,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,43; 502,01</t>
+          <t>-35,71; 734,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 195,44</t>
+          <t>-23,82; 191,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-38,22; 72,08</t>
+          <t>-37,18; 79,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 21,65</t>
+          <t>-2,46; 21,81</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 1,65</t>
+          <t>-26,82; 0,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 16,77</t>
+          <t>-16,99; 18,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 25,36</t>
+          <t>-15,68; 25,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,41; 10,83</t>
+          <t>-19,28; 10,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,4; 7,25</t>
+          <t>-64,95; 3,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 55,36</t>
+          <t>-34,46; 58,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,83; 96,23</t>
+          <t>-36,18; 100,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 16,73</t>
+          <t>-24,97; 15,27</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 5,45</t>
+          <t>-15,42; 6,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 10,05</t>
+          <t>-11,04; 9,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 7,69</t>
+          <t>-11,0; 8,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 13,9</t>
+          <t>-5,4; 13,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 17,87</t>
+          <t>-36,0; 20,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 30,69</t>
+          <t>-26,46; 29,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-33,02; 33,55</t>
+          <t>-33,4; 32,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 18,84</t>
+          <t>-6,28; 18,6</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 10,12</t>
+          <t>-12,93; 10,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 2,72</t>
+          <t>-15,46; 3,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 8,28</t>
+          <t>-10,47; 7,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 7,33</t>
+          <t>-5,12; 8,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,76; 29,51</t>
+          <t>-26,73; 30,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 10,12</t>
+          <t>-42,93; 12,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 30,01</t>
+          <t>-27,56; 26,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 8,8</t>
+          <t>-5,75; 10,51</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,33; -0,18</t>
+          <t>-8,94; 0,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 4,83</t>
+          <t>-4,79; 5,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 5,38</t>
+          <t>-3,83; 5,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 7,88</t>
+          <t>-2,77; 7,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-23,34; -0,03</t>
+          <t>-22,7; 1,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 14,58</t>
+          <t>-12,64; 16,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 17,29</t>
+          <t>-10,79; 18,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 10,85</t>
+          <t>-3,51; 10,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,06</t>
+          <t>-4,1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-4,19%</t>
+          <t>-8,55%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 8,66</t>
+          <t>-19,13; 9,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 24,27</t>
+          <t>-15,35; 23,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 11,02</t>
+          <t>-21,65; 11,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 13,28</t>
+          <t>-18,23; 10,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,25; 37,03</t>
+          <t>-50,27; 39,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 90,69</t>
+          <t>-35,93; 83,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-39,2; 28,58</t>
+          <t>-40,17; 29,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,83; 31,57</t>
+          <t>-32,91; 24,02</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 2,8</t>
+          <t>-24,47; 3,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 13,9</t>
+          <t>-16,82; 13,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 20,85</t>
+          <t>-4,68; 21,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 20,39</t>
+          <t>-10,4; 13,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 7,32</t>
+          <t>-45,92; 9,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,15; 45,29</t>
+          <t>-36,61; 44,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 84,26</t>
+          <t>-13,42; 85,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 29,35</t>
+          <t>-12,22; 19,35</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,09</t>
+          <t>-3,22</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-4,09%</t>
+          <t>-4,26%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 13,58</t>
+          <t>-12,23; 12,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 21,17</t>
+          <t>-7,39; 21,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 15,37</t>
+          <t>-14,09; 13,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 9,43</t>
+          <t>-15,23; 8,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 64,99</t>
+          <t>-38,92; 58,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 84,23</t>
+          <t>-19,39; 87,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-40,73; 68,24</t>
+          <t>-40,4; 58,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 13,21</t>
+          <t>-19,06; 12,59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,38</t>
+          <t>12,46</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 9,49</t>
+          <t>-19,41; 7,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 21,58</t>
+          <t>-11,36; 20,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 21,35</t>
+          <t>-12,39; 22,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 37,65</t>
+          <t>-4,09; 34,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,73; 31,02</t>
+          <t>-41,43; 21,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,37; 81,66</t>
+          <t>-26,62; 72,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 84,31</t>
+          <t>-29,4; 86,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 95,76</t>
+          <t>-5,47; 85,42</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>1,98</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 58,69</t>
+          <t>-17,14; 53,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 40,07</t>
+          <t>-11,12; 40,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 20,89</t>
+          <t>-17,7; 19,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 17,69</t>
+          <t>-3,51; 9,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,71; 734,74</t>
+          <t>-41,91; 583,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 191,76</t>
+          <t>-28,65; 204,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 79,08</t>
+          <t>-38,41; 66,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 21,81</t>
+          <t>-3,44; 10,61</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,77</t>
+          <t>-4,26</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-5,3%</t>
+          <t>-6,03%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 0,95</t>
+          <t>-26,74; 2,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 18,78</t>
+          <t>-15,97; 18,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 25,54</t>
+          <t>-17,45; 25,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 10,11</t>
+          <t>-18,67; 9,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,95; 3,31</t>
+          <t>-64,27; 11,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,46; 58,12</t>
+          <t>-33,22; 57,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,18; 100,41</t>
+          <t>-36,96; 102,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 15,27</t>
+          <t>-25,0; 14,49</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>-0,65</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>-0,77%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 6,27</t>
+          <t>-14,14; 6,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 9,54</t>
+          <t>-11,18; 9,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 8,12</t>
+          <t>-11,46; 7,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 13,94</t>
+          <t>-9,08; 7,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 20,08</t>
+          <t>-34,48; 20,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 29,67</t>
+          <t>-26,85; 30,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-33,4; 32,08</t>
+          <t>-33,9; 29,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 18,6</t>
+          <t>-10,3; 9,55</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,42</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 10,55</t>
+          <t>-13,69; 9,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 3,3</t>
+          <t>-16,38; 1,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 7,4</t>
+          <t>-9,52; 7,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 8,62</t>
+          <t>-5,19; 8,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 30,26</t>
+          <t>-28,79; 27,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,93; 12,76</t>
+          <t>-46,11; 4,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,56; 26,43</t>
+          <t>-25,96; 26,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 10,51</t>
+          <t>-5,87; 10,28</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 0,45</t>
+          <t>-9,27; 0,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 5,31</t>
+          <t>-4,78; 5,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 5,72</t>
+          <t>-4,09; 5,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 7,81</t>
+          <t>-3,56; 5,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 1,33</t>
+          <t>-23,54; 1,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 16,28</t>
+          <t>-12,67; 15,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 18,44</t>
+          <t>-11,5; 16,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 10,78</t>
+          <t>-4,55; 6,81</t>
         </is>
       </c>
     </row>
